--- a/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,440 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 먼저, 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 그게… 요즘 제가 저 같지 않다는 느낌이 들어요. 예전에는 등산도 하고, 코칭도 하고, 기타도 치고, 사람들이랑 연락도 자주 했는데, 지금은 그런 걸 거의 안 해요. 연락 온 것도 다시 전화를 안 해요. 어떤 날은 그냥 임대 주택에 몇 시간씩 앉아만 있어요, 해야 할 일이 있다는 건 아는데, 시작할 힘이 안 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌이 든 지는 얼마나 되셨나요—몇 주, 몇 달, 아니면 그보다 더 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 더 오래됐어요. 한… 1년 2개월쯤 됐을 거예요. 이혼하고 그 작은 임대 주택으로 이사한 후부터 일들이 흐트러지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 14개월 동안 기분이랑 의욕 저하가 계속 비슷한 상태로 이어졌나요, 아니면 눈에 띄게 더 나빠지거나 나아진 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 대체로 비슷했던 것 같아요. 어떤 날이 조금 더 안 좋을 수는 있는데, 전반적으로는 그냥 저 같지 않다는 이 꾸준한 느낌이에요. 등산도 안 하고, 코칭도 그만뒀고, 기타도 거의 안 만지고, 다시 연락도 안 해요. 어떤 날은 그냥 그 임대 주택에 몇 시간씩 앉아서 뭔가 해야 한다는 건 아는데 시작을 못 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 1년쯤 동안 수면이나 식욕의 변화, 집중력 문제, 무가치감이나 죄책감, 혹은 살고 싶지 않다는 생각 같은 것도 알아차리셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 집중력은 별로 안 좋은데, 그게 같은 건지는 모르겠어요. 수면이랑 식욕은… 딱히 신경 써서 지켜보지 않았어요. 그런 것들을 명확히 알아차리진 못한 것 같아요. 그리고 살고 싶지 않다는 생각은—뭐라 답해야 할지 잘 모르겠어요, 딱히 거기에 집중하지 않았다는 것 말고는요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 예전에 비해 수면 양이나 질에 변화를 느끼신 적이 있나요—잠들기 힘들다거나, 계속 깨어 있다거나, 아니면 평소보다 훨씬 더 많이 잔다거나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 수면을 딱히 신경 써서 기록하지 않았고, 눈에 띄게 뚜렷한 변화는 없는 것 같아요, 어느 쪽으로든요. 어떤 밤은 좀 이상하다고 느껴지긴 하는데, 그게 예전보다 더 많은 건지 적은 건지는 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 변화를 느끼신 적이 있나요—평소보다 더 많이 먹거나 적게 먹거나, 아니면 의도치 않게 살이 찌거나 빠졌다거나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 딱히 지켜보지 않았고, 먹는 양이 눈에 띄게 달라졌다고는 말 못 하겠어요. 크게 늘거나 줄었다고 눈에 띄는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 1년 동안 예전보다 자신이 무가치하다고 느끼거나, 지나치게 자책하는 일이 많아졌나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까 가끔 스스로한테 답답함을 느끼긴 하는데, 예전보다 무가치하다고 느끼거나 계속 자책한다고는 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 1년 동안 별로 신체 활동을 안 했는데도 거의 매일 유난히 피곤하거나 기운이 없다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 지치는 날들이 있긴 한데, 그게 거의 매일이라거나 예전이랑 확실히 다르다고는 말 못 하겠어요. 딱히 눈에 띄는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 집중이나 결정을 내리는 데 어려움이 거의 매일 있다고 말씀하시겠어요, 아니면 가끔씩 가볍게 있는 편이신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 집중을 못 하긴 하는데, 그게 거의 매일 일어난다고는 말 못 하겠어요. 왔다 갔다 하는 느낌에 더 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 등산이나 코칭, 기타 연주 같은 것들에 대한 흥미 저하가 지난 1년 동안 거의 매일 있었다고 하시겠어요, 아니면 왔다 갔다 하는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 거의 매일 있는 것 같아요, 네. 그냥 제가 저 같지 않다는 느낌이에요. 등산도 그만뒀고, 코칭도 그만뒀고, 기타도 거의 안 치고, 다시 연락해야 할 사람들한테 연락도 안 해요. 어떤 날은 그냥 임대 주택에 몇 시간씩 앉아서, 할 일이 있다는 건 아는데 시작을 못 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 지난 1년 동안 이게 직장이나 일상적인 책임을 다하는 능력에 영향을 미쳤나요, 아니면 이런 기분에도 불구하고 기본적인 의무는 대체로 지켜오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 많이 영향이 있었어요. 순찰 중에 직원들이랑 주변 사람들을 놀라게 한 일이 있고 나서 경비 일에서 정직당했어요. 그 이후로 코칭이랑 자원봉사, 심지어 저한테 의지하던 사람들한테서도 좀 물러났어요. 예전처럼 잘 챙기지는 못하고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 흥미를 잃는 것 외에도, 지난 1년 동안 거의 매일 슬프거나 우울하거나 기분이 가라앉는다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 거의 매일 우울하다고 표현해야 할지 모르겠어요. 그냥 뭔가 이상하고 저 같지 않다고 느끼긴 하는데, 매일 슬프거나 가라앉는다고는… 잘 모르겠어요. 딱히 그렇게 기록해 오지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 지난 1년을 돌아보면, 기분, 수면, 식욕, 에너지가 전반적으로 느껴온 것보다 눈에 띄게 더 나빠졌던 적어도 2주 이상의 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 모든 게 한꺼번에 떨어진 명확한 2주 정도의 시기를 콕 집기는 어려워요. 그냥… 전반적으로 계속 안 좋은 상태였고, 어떤 날은 더 나빴는데, 말씀하시는 것 같은 특정 시기는 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 지난 1년 동안, 매일은 아니더라도 안 그런 날보다 기분이 가라앉거나 낮았던 날이 더 많았다고 하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 안 좋은 날이 많긴 했는데, 안 그런 날보다 가라앉는 날이 더 많았는지는 모르겠어요. '기분이 가라앉는 것'을 그냥 뭔가 이상하고 저 같지 않다는 느낌이랑 구분하기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 약 14개월 전 이혼하고 임대 주택으로 이사하기 전에도 이미 이런 기분을 느끼기 시작했다고 생각하시나요, 아니면 정말 그때부터 시작된 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 정말 그때부터 시작된 것 같아요. 이혼하고 그 작은 임대 주택으로 이사한 후부터 일들이 흐트러지기 시작했어요. 그게 한 1년 2개월쯤 전이었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[16번째 턴 · 의사 질문] </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 죄송한데, 지금 뭘 물어보시는 건지 잘 모르겠어요. 질문을 다시 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 사람들을 놀라게 했던 순찰 사건 이후로, 그 일에 대한 원치 않는 기억이나 플래시백, 악몽 같은 게 있었나요, 아니면 유난히 예민해지거나 쉽게 놀라게 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 그 일에 대한 플래시백이나 악몽은 없었던 것 같아요, 적어도 기억나는 건 없어요. 가끔 긴장되긴 하는데, 그게 특별히 그 순찰 사건 때문이라고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 지난 1년 동안 주변 사람들이 본인이 평소보다 움직이거나 말하거나 반응하는 게 더 느려졌다고 알아챈 적이 있나요, 아니면 반대로 거의 매일 유난히 안절부절못하거나 들썩거린다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네… 사람들이 알아챘어요. 순찰 중에 제가 스스로를 진정시키기도 전에 먼저 반응하기 시작했어요. 카운터 뒤에 웅크리고, 사람들한테 물러나라고 신호를 보내고, 뭔가 의미가 있는지 확인하려고 사람들이 마지막에 한 말을 반복하고, 같은 경로를 몇 번이고 왔다 갔다 하기도 했어요. 직원들이 저를 무서워하기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 그날 순찰 사건 이후로, 예를 들어 유난히 경계하거나, 사람들 말을 반복하거나, 예민해지는 것 같은 비슷한 행동을 다른 상황에서도 알아차리신 적이 있나요, 아니면 그건 주로 그 한 번의 사건에 국한된 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 그때 한순간에만 국한된 건 아니었어요. 순찰 사건 때 그게 정말 확실히 드러난 거예요. 생각할 새도 없이 반응했어요—카운터 뒤에 웅크리고, 사람들한테 물러나라고 손짓하고, 뭔가 의미가 있을까 싶어서 사람들이 방금 한 말을 반복하고, 그러고 나서 같은 경로를 계속 왔다 갔다 하고요. 사람들이 저를 무서워하기 시작했고, 그때서야 이게 정상이 아니라는 걸 깨달았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006) | 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 사람들이 한 말을 반복하거나 뭔가 '의미가 있는 것' 같다고 느꼈을 때에 대해 좀 더 말씀해 주시겠어요—평범한 것들 속에 숨겨진 메시지나 특별한 의미가 있다고 느끼셨나요, 아니면 다른 사람들은 눈치채지 못하는 뭔가 특이한 걸 보거나 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 네. 그러니까… 극단적으로 들린다는 건 아는데, 평범한 것들이 평범하지 않게 느껴졌어요. 몇 달 동안 제 임대 주택 맞은편에 사는 사람들이랑 직장의 몇몇 사람들이 어떻게든 제 순찰 경로를 추적하거나 제 자물쇠를 확인하고 있다고 확신했어요.
+같은 차들이 계속 나타나거나, 제가 방금 한 행동이랑 너무 딱 맞아떨어지는 사람들의 작은 말들 같은 거였어요. 저한테는 무작위로 느껴지지 않았어요. 신호를 보내거나 저를 시험하는 것처럼 느껴졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 제1형 양극성장애 (D008) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현병 (D005)
 인구통계: 성별 남성 / 나이 45 / 직업상태 protective service worker / 최종학력 학사
@@ -575,447 +1000,15 @@
 증상 지속 기간: 1 year and 2 months
 추가 요건: 
 주호소 증상 코드: S023
-배경 서술: 이혼 후 오렘의 더 작은 임대 주택으로 이사한 뒤, 마이클은 탈출로를 파악하고 자물쇠를 조정하고 낯선 동네에 맞춰 일상을 재정비하면서 새 거처를 안전하게 느끼도록 만들려 했다. 이후 1년 2개월에 걸쳐, 그의 직업적 경계심은 임상적으로 유의미한 수준으로 발전했다—고정된 위협 관련 믿음, 외부 자극 없이 생생하게 느껴지는 지각 경험, 보안 업무 중 점점 부적절해지는 반응, 그리고 사회적·창의적 활동에 대한 뚜렷한 흥미 상실이 그가 평소 즐기던 등산, 코칭, 음악, 자원봉사 활동을 압도해 버렸다. 이러한 쇠퇴는 그의 근무 판단력에 지장을 주었고, 정기 순찰 중 그의 행동이 직원들과 행인들을 놀라게 한 사건 이후 정직 처분을 받게 되었다. 그는 직장의 안전 프로토콜을 통해 응급 정신과 평가를 받게 되었고, 입원 후 후속 진료가 마련되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 먼저, 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 그게… 요즘 제가 저 같지 않다는 느낌이 들어요. 예전에는 등산도 하고, 코칭도 하고, 기타도 치고, 사람들이랑 연락도 자주 했는데, 지금은 그런 걸 거의 안 해요. 연락 온 것도 다시 전화를 안 해요. 어떤 날은 그냥 임대 주택에 몇 시간씩 앉아만 있어요, 해야 할 일이 있다는 건 아는데, 시작할 힘이 안 나요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌이 든 지는 얼마나 되셨나요—몇 주, 몇 달, 아니면 그보다 더 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 더 오래됐어요. 한… 1년 2개월쯤 됐을 거예요. 이혼하고 그 작은 임대 주택으로 이사한 후부터 일들이 흐트러지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 14개월 동안 기분이랑 의욕 저하가 계속 비슷한 상태로 이어졌나요, 아니면 눈에 띄게 더 나빠지거나 나아진 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 대체로 비슷했던 것 같아요. 어떤 날이 조금 더 안 좋을 수는 있는데, 전반적으로는 그냥 저 같지 않다는 이 꾸준한 느낌이에요. 등산도 안 하고, 코칭도 그만뒀고, 기타도 거의 안 만지고, 다시 연락도 안 해요. 어떤 날은 그냥 그 임대 주택에 몇 시간씩 앉아서 뭔가 해야 한다는 건 아는데 시작을 못 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 1년쯤 동안 수면이나 식욕의 변화, 집중력 문제, 무가치감이나 죄책감, 혹은 살고 싶지 않다는 생각 같은 것도 알아차리셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 집중력은 별로 안 좋은데, 그게 같은 건지는 모르겠어요. 수면이랑 식욕은… 딱히 신경 써서 지켜보지 않았어요. 그런 것들을 명확히 알아차리진 못한 것 같아요. 그리고 살고 싶지 않다는 생각은—뭐라 답해야 할지 잘 모르겠어요, 딱히 거기에 집중하지 않았다는 것 말고는요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 예전에 비해 수면 양이나 질에 변화를 느끼신 적이 있나요—잠들기 힘들다거나, 계속 깨어 있다거나, 아니면 평소보다 훨씬 더 많이 잔다거나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 수면을 딱히 신경 써서 기록하지 않았고, 눈에 띄게 뚜렷한 변화는 없는 것 같아요, 어느 쪽으로든요. 어떤 밤은 좀 이상하다고 느껴지긴 하는데, 그게 예전보다 더 많은 건지 적은 건지는 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 식욕이나 체중에 변화를 느끼신 적이 있나요—평소보다 더 많이 먹거나 적게 먹거나, 아니면 의도치 않게 살이 찌거나 빠졌다거나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 딱히 지켜보지 않았고, 먹는 양이 눈에 띄게 달라졌다고는 말 못 하겠어요. 크게 늘거나 줄었다고 눈에 띄는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 1년 동안 예전보다 자신이 무가치하다고 느끼거나, 지나치게 자책하는 일이 많아졌나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까 가끔 스스로한테 답답함을 느끼긴 하는데, 예전보다 무가치하다고 느끼거나 계속 자책한다고는 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 1년 동안 별로 신체 활동을 안 했는데도 거의 매일 유난히 피곤하거나 기운이 없다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 지치는 날들이 있긴 한데, 그게 거의 매일이라거나 예전이랑 확실히 다르다고는 말 못 하겠어요. 딱히 눈에 띄는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 집중이나 결정을 내리는 데 어려움이 거의 매일 있다고 말씀하시겠어요, 아니면 가끔씩 가볍게 있는 편이신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 집중을 못 하긴 하는데, 그게 거의 매일 일어난다고는 말 못 하겠어요. 왔다 갔다 하는 느낌에 더 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 등산이나 코칭, 기타 연주 같은 것들에 대한 흥미 저하가 지난 1년 동안 거의 매일 있었다고 하시겠어요, 아니면 왔다 갔다 하는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 거의 매일 있는 것 같아요, 네. 그냥 제가 저 같지 않다는 느낌이에요. 등산도 그만뒀고, 코칭도 그만뒀고, 기타도 거의 안 치고, 다시 연락해야 할 사람들한테 연락도 안 해요. 어떤 날은 그냥 임대 주택에 몇 시간씩 앉아서, 할 일이 있다는 건 아는데 시작을 못 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 지난 1년 동안 이게 직장이나 일상적인 책임을 다하는 능력에 영향을 미쳤나요, 아니면 이런 기분에도 불구하고 기본적인 의무는 대체로 지켜오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 많이 영향이 있었어요. 순찰 중에 직원들이랑 주변 사람들을 놀라게 한 일이 있고 나서 경비 일에서 정직당했어요. 그 이후로 코칭이랑 자원봉사, 심지어 저한테 의지하던 사람들한테서도 좀 물러났어요. 예전처럼 잘 챙기지는 못하고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 흥미를 잃는 것 외에도, 지난 1년 동안 거의 매일 슬프거나 우울하거나 기분이 가라앉는다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 거의 매일 우울하다고 표현해야 할지 모르겠어요. 그냥 뭔가 이상하고 저 같지 않다고 느끼긴 하는데, 매일 슬프거나 가라앉는다고는… 잘 모르겠어요. 딱히 그렇게 기록해 오지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 지난 1년을 돌아보면, 기분, 수면, 식욕, 에너지가 전반적으로 느껴온 것보다 눈에 띄게 더 나빠졌던 적어도 2주 이상의 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 모든 게 한꺼번에 떨어진 명확한 2주 정도의 시기를 콕 집기는 어려워요. 그냥… 전반적으로 계속 안 좋은 상태였고, 어떤 날은 더 나빴는데, 말씀하시는 것 같은 특정 시기는 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 지난 1년 동안, 매일은 아니더라도 안 그런 날보다 기분이 가라앉거나 낮았던 날이 더 많았다고 하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 안 좋은 날이 많긴 했는데, 안 그런 날보다 가라앉는 날이 더 많았는지는 모르겠어요. '기분이 가라앉는 것'을 그냥 뭔가 이상하고 저 같지 않다는 느낌이랑 구분하기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 약 14개월 전 이혼하고 임대 주택으로 이사하기 전에도 이미 이런 기분을 느끼기 시작했다고 생각하시나요, 아니면 정말 그때부터 시작된 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 정말 그때부터 시작된 것 같아요. 이혼하고 그 작은 임대 주택으로 이사한 후부터 일들이 흐트러지기 시작했어요. 그게 한 1년 2개월쯤 전이었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[16번째 턴 · 의사 질문] </t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 죄송한데, 지금 뭘 물어보시는 건지 잘 모르겠어요. 질문을 다시 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 사람들을 놀라게 했던 순찰 사건 이후로, 그 일에 대한 원치 않는 기억이나 플래시백, 악몽 같은 게 있었나요, 아니면 유난히 예민해지거나 쉽게 놀라게 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 잘 모르겠어요. 그 일에 대한 플래시백이나 악몽은 없었던 것 같아요, 적어도 기억나는 건 없어요. 가끔 긴장되긴 하는데, 그게 특별히 그 순찰 사건 때문이라고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 지난 1년 동안 주변 사람들이 본인이 평소보다 움직이거나 말하거나 반응하는 게 더 느려졌다고 알아챈 적이 있나요, 아니면 반대로 거의 매일 유난히 안절부절못하거나 들썩거린다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네… 사람들이 알아챘어요. 순찰 중에 제가 스스로를 진정시키기도 전에 먼저 반응하기 시작했어요. 카운터 뒤에 웅크리고, 사람들한테 물러나라고 신호를 보내고, 뭔가 의미가 있는지 확인하려고 사람들이 마지막에 한 말을 반복하고, 같은 경로를 몇 번이고 왔다 갔다 하기도 했어요. 직원들이 저를 무서워하기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 그날 순찰 사건 이후로, 예를 들어 유난히 경계하거나, 사람들 말을 반복하거나, 예민해지는 것 같은 비슷한 행동을 다른 상황에서도 알아차리신 적이 있나요, 아니면 그건 주로 그 한 번의 사건에 국한된 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 그때 한순간에만 국한된 건 아니었어요. 순찰 사건 때 그게 정말 확실히 드러난 거예요. 생각할 새도 없이 반응했어요—카운터 뒤에 웅크리고, 사람들한테 물러나라고 손짓하고, 뭔가 의미가 있을까 싶어서 사람들이 방금 한 말을 반복하고, 그러고 나서 같은 경로를 계속 왔다 갔다 하고요. 사람들이 저를 무서워하기 시작했고, 그때서야 이게 정상이 아니라는 걸 깨달았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006) | 저확률: 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 사람들이 한 말을 반복하거나 뭔가 '의미가 있는 것' 같다고 느꼈을 때에 대해 좀 더 말씀해 주시겠어요—평범한 것들 속에 숨겨진 메시지나 특별한 의미가 있다고 느끼셨나요, 아니면 다른 사람들은 눈치채지 못하는 뭔가 특이한 걸 보거나 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 네. 그러니까… 극단적으로 들린다는 건 아는데, 평범한 것들이 평범하지 않게 느껴졌어요. 몇 달 동안 제 임대 주택 맞은편에 사는 사람들이랑 직장의 몇몇 사람들이 어떻게든 제 순찰 경로를 추적하거나 제 자물쇠를 확인하고 있다고 확신했어요.
-같은 차들이 계속 나타나거나, 제가 방금 한 행동이랑 너무 딱 맞아떨어지는 사람들의 작은 말들 같은 거였어요. 저한테는 무작위로 느껴지지 않았어요. 신호를 보내거나 저를 시험하는 것처럼 느껴졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 이혼 후 오렘의 더 작은 임대 주택으로 이사한 뒤, 마이클은 탈출로를 파악하고 자물쇠를 조정하고 낯선 동네에 맞춰 일상을 재정비하면서 새 거처를 안전하게 느끼도록 만들려 했다. 이후 1년 2개월에 걸쳐, 그의 직업적 경계심은 임상적으로 유의미한 수준으로 발전했다—고정된 위협 관련 믿음, 외부 자극 없이 생생하게 느껴지는 지각 경험, 보안 업무 중 점점 부적절해지는 반응, 그리고 사회적·창의적 활동에 대한 뚜렷한 흥미 상실이 그가 평소 즐기던 등산, 코칭, 음악, 자원봉사 활동을 압도해 버렸다. 이러한 쇠퇴는 그의 근무 판단력에 지장을 주었고, 정기 순찰 중 그의 행동이 직원들과 행인들을 놀라게 한 사건 이후 정직 처분을 받게 되었다. 그는 직장의 안전 프로토콜을 통해 응급 정신과 평가를 받게 되었고, 입원 후 후속 진료가 마련되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>의사의 최종 진단: None (None, ICD: {
   "diagnosis": "F20.9",
@@ -1045,47 +1038,24 @@
       {
         "group": "depressive_symptoms_subsyndromal",
         "confirmed_symptoms": [
-          "Uncertain/mild concentration diffic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
-  누락: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.</t>
+          "Uncertain/mild concentration diffic)
+지속 기간 요건: 없음
+기능적 손상 요건: 없음
+추가 요건: None
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
@@ -986,6 +986,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1051,11 +1056,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S003_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0394</v>
+        <v>0.0611</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0478</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5658</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
